--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0584</v>
+        <v>0.0114</v>
       </c>
       <c r="E2">
-        <v>0.0131</v>
+        <v>0.216</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.00409898670095335</v>
+        <v>0.001743628817909475</v>
       </c>
       <c r="J2">
-        <v>0.003795358056438287</v>
+        <v>0.001631562577379759</v>
       </c>
       <c r="K2">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="L2">
-        <v>0.120353982300885</v>
+        <v>0.1946938775510204</v>
       </c>
       <c r="M2">
-        <v>0.3429</v>
+        <v>0.416</v>
       </c>
       <c r="N2">
-        <v>0.027432</v>
+        <v>0.01363934426229508</v>
       </c>
       <c r="O2">
-        <v>0.1260661764705882</v>
+        <v>0.08721174004192872</v>
       </c>
       <c r="P2">
-        <v>0.3429</v>
+        <v>0.416</v>
       </c>
       <c r="Q2">
-        <v>0.027432</v>
+        <v>0.01363934426229508</v>
       </c>
       <c r="R2">
-        <v>0.1260661764705882</v>
+        <v>0.08721174004192872</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>40.8</v>
+        <v>17.5</v>
       </c>
       <c r="V2">
-        <v>3.264</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="W2">
-        <v>0.1007407407407407</v>
+        <v>0.1495297805642633</v>
       </c>
       <c r="X2">
-        <v>0.04819451030275163</v>
+        <v>0.06405161295976466</v>
       </c>
       <c r="Y2">
-        <v>0.05254623043798911</v>
+        <v>0.08547816760449864</v>
       </c>
       <c r="Z2">
-        <v>0.667615616236342</v>
+        <v>1.322079970670264</v>
       </c>
       <c r="AA2">
-        <v>0.002533840307686612</v>
+        <v>0.002157056204448934</v>
       </c>
       <c r="AB2">
-        <v>0.03385413349240789</v>
+        <v>0.06308012746408309</v>
       </c>
       <c r="AC2">
-        <v>-0.03132029318472128</v>
+        <v>-0.06092307125963416</v>
       </c>
       <c r="AD2">
-        <v>33.3</v>
+        <v>39.5</v>
       </c>
       <c r="AE2">
-        <v>0.1118145027922714</v>
+        <v>0.2214054698060892</v>
       </c>
       <c r="AF2">
-        <v>33.41181450279227</v>
+        <v>39.72140546980609</v>
       </c>
       <c r="AG2">
-        <v>-7.388185497207729</v>
+        <v>22.22140546980609</v>
       </c>
       <c r="AH2">
-        <v>0.727738924384272</v>
+        <v>0.5656595051616499</v>
       </c>
       <c r="AI2">
-        <v>0.5115738210176939</v>
+        <v>0.5477197416746686</v>
       </c>
       <c r="AJ2">
-        <v>-1.445315649300658</v>
+        <v>0.4214873498115</v>
       </c>
       <c r="AK2">
-        <v>-0.3014132428411655</v>
+        <v>0.4038683723192141</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>289.5652173913043</v>
+        <v>454.0229885057472</v>
       </c>
       <c r="AP2">
-        <v>-64.24509128006721</v>
+        <v>255.4184536759321</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0584</v>
+        <v>0.0114</v>
       </c>
       <c r="E3">
-        <v>0.0131</v>
+        <v>0.216</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.00409898670095335</v>
+        <v>0.001743628817909475</v>
       </c>
       <c r="J3">
-        <v>0.003795358056438287</v>
+        <v>0.001631562577379759</v>
       </c>
       <c r="K3">
-        <v>2.72</v>
+        <v>4.77</v>
       </c>
       <c r="L3">
-        <v>0.120353982300885</v>
+        <v>0.1946938775510204</v>
       </c>
       <c r="M3">
-        <v>0.3429</v>
+        <v>0.416</v>
       </c>
       <c r="N3">
-        <v>0.027432</v>
+        <v>0.01363934426229508</v>
       </c>
       <c r="O3">
-        <v>0.1260661764705882</v>
+        <v>0.08721174004192872</v>
       </c>
       <c r="P3">
-        <v>0.3429</v>
+        <v>0.416</v>
       </c>
       <c r="Q3">
-        <v>0.027432</v>
+        <v>0.01363934426229508</v>
       </c>
       <c r="R3">
-        <v>0.1260661764705882</v>
+        <v>0.08721174004192872</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40.8</v>
+        <v>17.5</v>
       </c>
       <c r="V3">
-        <v>3.264</v>
+        <v>0.5737704918032787</v>
       </c>
       <c r="W3">
-        <v>0.1007407407407407</v>
+        <v>0.1495297805642633</v>
       </c>
       <c r="X3">
-        <v>0.04819451030275163</v>
+        <v>0.06405161295976466</v>
       </c>
       <c r="Y3">
-        <v>0.05254623043798911</v>
+        <v>0.08547816760449864</v>
       </c>
       <c r="Z3">
-        <v>0.667615616236342</v>
+        <v>1.322079970670264</v>
       </c>
       <c r="AA3">
-        <v>0.002533840307686612</v>
+        <v>0.002157056204448934</v>
       </c>
       <c r="AB3">
-        <v>0.03385413349240789</v>
+        <v>0.06308012746408309</v>
       </c>
       <c r="AC3">
-        <v>-0.03132029318472128</v>
+        <v>-0.06092307125963416</v>
       </c>
       <c r="AD3">
-        <v>33.3</v>
+        <v>39.5</v>
       </c>
       <c r="AE3">
-        <v>0.1118145027922714</v>
+        <v>0.2214054698060892</v>
       </c>
       <c r="AF3">
-        <v>33.41181450279227</v>
+        <v>39.72140546980609</v>
       </c>
       <c r="AG3">
-        <v>-7.388185497207729</v>
+        <v>22.22140546980609</v>
       </c>
       <c r="AH3">
-        <v>0.727738924384272</v>
+        <v>0.5656595051616499</v>
       </c>
       <c r="AI3">
-        <v>0.5115738210176939</v>
+        <v>0.5477197416746686</v>
       </c>
       <c r="AJ3">
-        <v>-1.445315649300658</v>
+        <v>0.4214873498115</v>
       </c>
       <c r="AK3">
-        <v>-0.3014132428411655</v>
+        <v>0.4038683723192141</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>289.5652173913043</v>
+        <v>454.0229885057472</v>
       </c>
       <c r="AP3">
-        <v>-64.24509128006721</v>
+        <v>255.4184536759321</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0114</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.216</v>
+        <v>0.0733</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001743628817909475</v>
+        <v>0.001377958231941321</v>
       </c>
       <c r="J2">
-        <v>0.001631562577379759</v>
+        <v>0.001174291968631752</v>
       </c>
       <c r="K2">
-        <v>4.77</v>
+        <v>5.21</v>
       </c>
       <c r="L2">
-        <v>0.1946938775510204</v>
+        <v>0.1335897435897436</v>
       </c>
       <c r="M2">
-        <v>0.416</v>
+        <v>0.034</v>
       </c>
       <c r="N2">
-        <v>0.01363934426229508</v>
+        <v>0.001504424778761062</v>
       </c>
       <c r="O2">
-        <v>0.08721174004192872</v>
+        <v>0.006525911708253359</v>
       </c>
       <c r="P2">
-        <v>0.416</v>
+        <v>0.034</v>
       </c>
       <c r="Q2">
-        <v>0.01363934426229508</v>
+        <v>0.001504424778761062</v>
       </c>
       <c r="R2">
-        <v>0.08721174004192872</v>
+        <v>0.006525911708253359</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>17.5</v>
+        <v>21.9</v>
       </c>
       <c r="V2">
-        <v>0.5737704918032787</v>
+        <v>0.9690265486725662</v>
       </c>
       <c r="W2">
-        <v>0.1495297805642633</v>
+        <v>0.1593272171253823</v>
       </c>
       <c r="X2">
-        <v>0.06405161295976466</v>
+        <v>0.08232110478735885</v>
       </c>
       <c r="Y2">
-        <v>0.08547816760449864</v>
+        <v>0.0770061123380234</v>
       </c>
       <c r="Z2">
-        <v>1.322079970670264</v>
+        <v>0.824414539490034</v>
       </c>
       <c r="AA2">
-        <v>0.002157056204448934</v>
+        <v>0.0009681033725463912</v>
       </c>
       <c r="AB2">
-        <v>0.06308012746408309</v>
+        <v>0.06490064702822244</v>
       </c>
       <c r="AC2">
-        <v>-0.06092307125963416</v>
+        <v>-0.06393254365567605</v>
       </c>
       <c r="AD2">
-        <v>39.5</v>
+        <v>52.1</v>
       </c>
       <c r="AE2">
-        <v>0.2214054698060892</v>
+        <v>0.2862981447714423</v>
       </c>
       <c r="AF2">
-        <v>39.72140546980609</v>
+        <v>52.38629814477144</v>
       </c>
       <c r="AG2">
-        <v>22.22140546980609</v>
+        <v>30.48629814477145</v>
       </c>
       <c r="AH2">
-        <v>0.5656595051616499</v>
+        <v>0.6986116055980313</v>
       </c>
       <c r="AI2">
-        <v>0.5477197416746686</v>
+        <v>0.5627713120925513</v>
       </c>
       <c r="AJ2">
-        <v>0.4214873498115</v>
+        <v>0.5742780945401839</v>
       </c>
       <c r="AK2">
-        <v>0.4038683723192141</v>
+        <v>0.4282607599958564</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>454.0229885057472</v>
+        <v>469.3693693693694</v>
       </c>
       <c r="AP2">
-        <v>255.4184536759321</v>
+        <v>274.6513346375806</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0114</v>
+        <v>0.109</v>
       </c>
       <c r="E3">
-        <v>0.216</v>
+        <v>0.0733</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.001743628817909475</v>
+        <v>0.001377958231941321</v>
       </c>
       <c r="J3">
-        <v>0.001631562577379759</v>
+        <v>0.001174291968631752</v>
       </c>
       <c r="K3">
-        <v>4.77</v>
+        <v>5.21</v>
       </c>
       <c r="L3">
-        <v>0.1946938775510204</v>
+        <v>0.1335897435897436</v>
       </c>
       <c r="M3">
-        <v>0.416</v>
+        <v>0.034</v>
       </c>
       <c r="N3">
-        <v>0.01363934426229508</v>
+        <v>0.001504424778761062</v>
       </c>
       <c r="O3">
-        <v>0.08721174004192872</v>
+        <v>0.006525911708253359</v>
       </c>
       <c r="P3">
-        <v>0.416</v>
+        <v>0.034</v>
       </c>
       <c r="Q3">
-        <v>0.01363934426229508</v>
+        <v>0.001504424778761062</v>
       </c>
       <c r="R3">
-        <v>0.08721174004192872</v>
+        <v>0.006525911708253359</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>17.5</v>
+        <v>21.9</v>
       </c>
       <c r="V3">
-        <v>0.5737704918032787</v>
+        <v>0.9690265486725662</v>
       </c>
       <c r="W3">
-        <v>0.1495297805642633</v>
+        <v>0.1593272171253823</v>
       </c>
       <c r="X3">
-        <v>0.06405161295976466</v>
+        <v>0.08232110478735885</v>
       </c>
       <c r="Y3">
-        <v>0.08547816760449864</v>
+        <v>0.0770061123380234</v>
       </c>
       <c r="Z3">
-        <v>1.322079970670264</v>
+        <v>0.824414539490034</v>
       </c>
       <c r="AA3">
-        <v>0.002157056204448934</v>
+        <v>0.0009681033725463912</v>
       </c>
       <c r="AB3">
-        <v>0.06308012746408309</v>
+        <v>0.06490064702822244</v>
       </c>
       <c r="AC3">
-        <v>-0.06092307125963416</v>
+        <v>-0.06393254365567605</v>
       </c>
       <c r="AD3">
-        <v>39.5</v>
+        <v>52.1</v>
       </c>
       <c r="AE3">
-        <v>0.2214054698060892</v>
+        <v>0.2862981447714423</v>
       </c>
       <c r="AF3">
-        <v>39.72140546980609</v>
+        <v>52.38629814477144</v>
       </c>
       <c r="AG3">
-        <v>22.22140546980609</v>
+        <v>30.48629814477145</v>
       </c>
       <c r="AH3">
-        <v>0.5656595051616499</v>
+        <v>0.6986116055980313</v>
       </c>
       <c r="AI3">
-        <v>0.5477197416746686</v>
+        <v>0.5627713120925513</v>
       </c>
       <c r="AJ3">
-        <v>0.4214873498115</v>
+        <v>0.5742780945401839</v>
       </c>
       <c r="AK3">
-        <v>0.4038683723192141</v>
+        <v>0.4282607599958564</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>454.0229885057472</v>
+        <v>469.3693693693694</v>
       </c>
       <c r="AP3">
-        <v>255.4184536759321</v>
+        <v>274.6513346375806</v>
       </c>
     </row>
   </sheetData>
